--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F73E0C1-4B2C-43C2-9E62-AF5A65AF3BAF}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15CD0A9B-FB07-4C8F-AC0C-CAD50E6A0F71}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,6 +207,15 @@
   <si>
     <t>todays I have 4 class one lecture and 2 practical.</t>
   </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>today I habve 8 class 6 lecture 2 pratical many class fully exhausted</t>
+  </si>
 </sst>
 </file>
 
@@ -215,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,6 +319,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -358,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -396,15 +427,33 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -889,22 +938,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -913,8 +962,8 @@
       <c r="B2" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
@@ -930,33 +979,33 @@
       <c r="B3" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1044,34 +1093,60 @@
       <c r="M6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="N6" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14" t="str">
+    <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B7" s="24">
+        <v>380</v>
+      </c>
+      <c r="C7" s="24">
+        <v>50</v>
+      </c>
+      <c r="D7" s="24">
+        <v>150</v>
+      </c>
+      <c r="E7" s="25">
+        <v>40</v>
+      </c>
+      <c r="F7" s="25">
+        <v>400</v>
+      </c>
+      <c r="G7" s="25">
+        <v>8</v>
+      </c>
+      <c r="H7" s="25">
+        <v>30</v>
+      </c>
+      <c r="I7" s="26">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="14" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J7" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
+      <c r="A8" s="8">
+        <v>46247</v>
+      </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -1209,7 +1284,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="13"/>
       <c r="I14" s="14" t="str">
         <f t="shared" si="0"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15CD0A9B-FB07-4C8F-AC0C-CAD50E6A0F71}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B796AFF1-DD8B-4952-AB5D-E5F9704B5D9C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1147,20 +1147,28 @@
       <c r="A8" s="8">
         <v>46247</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="B8" s="13">
+        <v>380</v>
+      </c>
+      <c r="C8" s="13">
+        <v>45</v>
+      </c>
+      <c r="D8" s="13">
+        <v>160</v>
+      </c>
+      <c r="E8" s="13">
+        <v>45</v>
+      </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="14" t="str">
+      <c r="I8" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="14" t="str">
+        <v>630</v>
+      </c>
+      <c r="J8" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>810</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B796AFF1-DD8B-4952-AB5D-E5F9704B5D9C}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A01096-5C2E-4823-9CE7-BF737EFD6F90}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>today I habve 8 class 6 lecture 2 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>today I habve 6 class 4 lecture 2 pratical many class fully exhausted</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>46247</v>
       </c>
@@ -1159,21 +1165,35 @@
       <c r="E8" s="13">
         <v>45</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="F8" s="13">
+        <v>300</v>
+      </c>
+      <c r="G8" s="13">
+        <v>6</v>
+      </c>
+      <c r="H8" s="13">
+        <v>50</v>
+      </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>980</v>
       </c>
       <c r="J8" s="14">
         <f t="shared" si="1"/>
-        <v>810</v>
-      </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A01096-5C2E-4823-9CE7-BF737EFD6F90}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41CA4D9F-5094-4766-BA63-59555A76E441}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,21 @@
   </si>
   <si>
     <t>today I habve 6 class 4 lecture 2 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>today I habve 3 class 3 lecture 0 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>holiday on the occasion of independence day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Week end </t>
   </si>
 </sst>
 </file>
@@ -436,13 +451,6 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -460,6 +468,13 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,6 +572,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -944,74 +963,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="28">
         <v>12604714</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1107,45 +1126,45 @@
       <c r="A7" s="8">
         <v>46246</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="19">
         <v>380</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="19">
         <v>50</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="19">
         <v>150</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="20">
         <v>40</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="20">
         <v>400</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="20">
         <v>8</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="20">
         <v>30</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="21">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="21">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="28" t="s">
+      <c r="N7" s="23" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1191,78 +1210,152 @@
       <c r="M8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="28" t="s">
+      <c r="N8" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14" t="str">
+    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B9" s="13">
+        <v>360</v>
+      </c>
+      <c r="C9" s="13">
+        <v>45</v>
+      </c>
+      <c r="D9" s="13">
+        <v>180</v>
+      </c>
+      <c r="E9" s="13">
+        <v>40</v>
+      </c>
+      <c r="F9" s="13">
+        <v>150</v>
+      </c>
+      <c r="G9" s="13">
+        <v>3</v>
+      </c>
+      <c r="H9" s="13">
+        <v>60</v>
+      </c>
+      <c r="I9" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="14" t="str">
+        <v>835</v>
+      </c>
+      <c r="J9" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14" t="str">
+        <v>605</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B10" s="13">
+        <v>350</v>
+      </c>
+      <c r="C10" s="13">
+        <v>60</v>
+      </c>
+      <c r="D10" s="13">
+        <v>200</v>
+      </c>
+      <c r="E10" s="13">
+        <v>35</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>120</v>
+      </c>
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="14" t="str">
+        <v>765</v>
+      </c>
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16"/>
+        <v>675</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14" t="str">
+      <c r="A11" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B11" s="13">
+        <v>380</v>
+      </c>
+      <c r="C11" s="13">
+        <v>90</v>
+      </c>
+      <c r="D11" s="13">
+        <v>240</v>
+      </c>
+      <c r="E11" s="13">
+        <v>40</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <v>120</v>
+      </c>
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
+      <c r="A12" s="8">
+        <v>46251</v>
+      </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -1312,7 +1405,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="23"/>
+      <c r="G14" s="18"/>
       <c r="H14" s="13"/>
       <c r="I14" s="14" t="str">
         <f t="shared" si="0"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41CA4D9F-5094-4766-BA63-59555A76E441}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE883E56-9E53-4A27-8A8A-FF16BB20489B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,24 @@
   </si>
   <si>
     <t xml:space="preserve">Week end </t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>today I have 8 class 5lecture 3 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>today I have 5 class 1lecture 4 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>today I have 5 class 5 lecture 0 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>today I have 5 class 4lecture 1 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1352,139 +1370,281 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>46251</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14" t="str">
+      <c r="B12" s="13">
+        <v>300</v>
+      </c>
+      <c r="C12" s="13">
+        <v>60</v>
+      </c>
+      <c r="D12" s="13">
+        <v>120</v>
+      </c>
+      <c r="E12" s="13">
+        <v>30</v>
+      </c>
+      <c r="F12" s="13">
+        <v>250</v>
+      </c>
+      <c r="G12" s="13">
+        <v>5</v>
+      </c>
+      <c r="H12" s="13">
+        <v>30</v>
+      </c>
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="14" t="str">
+        <v>790</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14" t="str">
+        <v>650</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="13">
+        <v>320</v>
+      </c>
+      <c r="C13" s="13">
+        <v>60</v>
+      </c>
+      <c r="D13" s="13">
+        <v>60</v>
+      </c>
+      <c r="E13" s="13">
+        <v>20</v>
+      </c>
+      <c r="F13" s="13">
+        <v>250</v>
+      </c>
+      <c r="G13" s="13">
+        <v>5</v>
+      </c>
+      <c r="H13" s="13">
+        <v>45</v>
+      </c>
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="14" t="str">
+        <v>755</v>
+      </c>
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="16"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14" t="str">
+        <v>685</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B14" s="13">
+        <v>300</v>
+      </c>
+      <c r="C14" s="13">
+        <v>45</v>
+      </c>
+      <c r="D14" s="13">
+        <v>90</v>
+      </c>
+      <c r="E14" s="13">
+        <v>30</v>
+      </c>
+      <c r="F14" s="13">
+        <v>400</v>
+      </c>
+      <c r="G14" s="18">
+        <v>8</v>
+      </c>
+      <c r="H14" s="13">
+        <v>45</v>
+      </c>
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="14" t="str">
+        <v>910</v>
+      </c>
+      <c r="J14" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="16"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14" t="str">
+        <v>530</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="13">
+        <v>300</v>
+      </c>
+      <c r="C15" s="13">
+        <v>60</v>
+      </c>
+      <c r="D15" s="13">
+        <v>60</v>
+      </c>
+      <c r="E15" s="13">
+        <v>45</v>
+      </c>
+      <c r="F15" s="13">
+        <v>250</v>
+      </c>
+      <c r="G15" s="13">
+        <v>5</v>
+      </c>
+      <c r="H15" s="13">
+        <v>60</v>
+      </c>
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="14" t="str">
+        <v>775</v>
+      </c>
+      <c r="J15" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="16"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14" t="str">
+        <v>665</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B16" s="13">
+        <v>300</v>
+      </c>
+      <c r="C16" s="13">
+        <v>60</v>
+      </c>
+      <c r="D16" s="13">
+        <v>30</v>
+      </c>
+      <c r="E16" s="13">
+        <v>30</v>
+      </c>
+      <c r="F16" s="13">
+        <v>250</v>
+      </c>
+      <c r="G16" s="13">
+        <v>5</v>
+      </c>
+      <c r="H16" s="13">
+        <v>45</v>
+      </c>
+      <c r="I16" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="14" t="str">
+        <v>715</v>
+      </c>
+      <c r="J16" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="16"/>
+        <v>725</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N16" s="23" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14" t="str">
+      <c r="A17" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B17" s="13">
+        <v>350</v>
+      </c>
+      <c r="C17" s="13">
+        <v>45</v>
+      </c>
+      <c r="D17" s="13">
+        <v>120</v>
+      </c>
+      <c r="E17" s="13">
+        <v>25</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>180</v>
+      </c>
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="14" t="str">
+        <v>720</v>
+      </c>
+      <c r="J17" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE883E56-9E53-4A27-8A8A-FF16BB20489B}"/>
+  <xr:revisionPtr revIDLastSave="290" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E0BC7C-57FA-4F23-B430-529163CB5F61}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -25,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -118,6 +123,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
@@ -130,13 +138,22 @@
     <t>Name:</t>
   </si>
   <si>
+    <t>Lakshmi ganesh maddala</t>
+  </si>
+  <si>
     <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
   </si>
   <si>
+    <t>MCA</t>
+  </si>
+  <si>
     <t>Month:</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -187,22 +204,10 @@
     <t>Good</t>
   </si>
   <si>
-    <t>Medium</t>
+    <t>Neutral</t>
   </si>
   <si>
-    <t>5. GOOD PRACTICE</t>
-  </si>
-  <si>
-    <t>Lakshmi ganesh maddala</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
-    <t>Neutral</t>
+    <t>Medium</t>
   </si>
   <si>
     <t>todays I have 4 class one lecture and 2 practical.</t>
@@ -238,22 +243,31 @@
     <t xml:space="preserve">Week end </t>
   </si>
   <si>
+    <t>today I have 5 class 5 lecture 0 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>today I have 5 class 1lecture 4 pratical many class fully exhausted</t>
+  </si>
+  <si>
     <t>Unsatisfied</t>
   </si>
   <si>
     <t>today I have 8 class 5lecture 3 pratical many class fully exhausted</t>
   </si>
   <si>
-    <t>today I have 5 class 1lecture 4 pratical many class fully exhausted</t>
-  </si>
-  <si>
-    <t>today I have 5 class 5 lecture 0 pratical many class fully exhausted</t>
-  </si>
-  <si>
     <t>today I have 5 class 4lecture 1 pratical many class fully exhausted</t>
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>today I have 6 class 4lecture 2 pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>today I have 8 class 4lecture 14pratical many class fully exhausted</t>
+  </si>
+  <si>
+    <t>today I have 4 class 2lecture 2 pratical many class fully exhausted</t>
   </si>
 </sst>
 </file>
@@ -263,7 +277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,13 +501,13 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,10 +604,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -776,186 +786,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="22.9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="16.899999999999999">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1">
       <c r="A33" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -967,7 +977,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -980,9 +990,9 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -998,103 +1008,103 @@
       <c r="M1" s="25"/>
       <c r="N1" s="25"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
       <c r="E2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="28">
+        <v>33</v>
+      </c>
+      <c r="F2" s="24">
         <v>12604714</v>
       </c>
-      <c r="G2" s="28"/>
-    </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
       <c r="E3" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="G3" s="27"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-    </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
+      <c r="A4" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+    </row>
+    <row r="5" spans="1:14" ht="41.45">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.9">
       <c r="A6" s="8">
         <v>46245</v>
       </c>
@@ -1128,19 +1138,19 @@
         <v>610</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="N6" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="43.15">
       <c r="A7" s="8">
         <v>46246</v>
       </c>
@@ -1177,7 +1187,7 @@
         <v>57</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>58</v>
@@ -1186,7 +1196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="43.15">
       <c r="A8" s="8">
         <v>46247</v>
       </c>
@@ -1220,19 +1230,19 @@
         <v>460</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L8" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N8" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="43.15">
       <c r="A9" s="8">
         <v>46248</v>
       </c>
@@ -1266,7 +1276,7 @@
         <v>605</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>60</v>
@@ -1278,7 +1288,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="28.9">
       <c r="A10" s="8">
         <v>46249</v>
       </c>
@@ -1312,7 +1322,7 @@
         <v>675</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>64</v>
@@ -1324,7 +1334,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14">
       <c r="A11" s="8">
         <v>46250</v>
       </c>
@@ -1358,19 +1368,19 @@
         <v>570</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L11" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N11" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="43.15">
       <c r="A12" s="8">
         <v>46251</v>
       </c>
@@ -1404,19 +1414,19 @@
         <v>650</v>
       </c>
       <c r="K12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>50</v>
-      </c>
       <c r="N12" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="43.15">
       <c r="A13" s="8">
         <v>46252</v>
       </c>
@@ -1450,19 +1460,19 @@
         <v>685</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L13" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="43.15">
       <c r="A14" s="8">
         <v>46253</v>
       </c>
@@ -1499,16 +1509,16 @@
         <v>57</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="43.15">
       <c r="A15" s="8">
         <v>46254</v>
       </c>
@@ -1542,19 +1552,19 @@
         <v>665</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L15" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N15" s="23" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="43.15">
       <c r="A16" s="8">
         <v>46255</v>
       </c>
@@ -1588,7 +1598,7 @@
         <v>725</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L16" s="15" t="s">
         <v>64</v>
@@ -1600,7 +1610,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15">
       <c r="A17" s="8">
         <v>46256</v>
       </c>
@@ -1646,206 +1656,424 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14" t="str">
+    <row r="18" spans="1:14" ht="15">
+      <c r="A18" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B18" s="13">
+        <v>300</v>
+      </c>
+      <c r="C18" s="13">
+        <v>30</v>
+      </c>
+      <c r="D18" s="13">
+        <v>90</v>
+      </c>
+      <c r="E18" s="13">
+        <v>30</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
+        <v>200</v>
+      </c>
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="str">
+        <v>650</v>
+      </c>
+      <c r="J18" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="16"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14" t="str">
+        <v>790</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="43.5">
+      <c r="A19" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B19" s="13">
+        <v>300</v>
+      </c>
+      <c r="C19" s="13">
+        <v>40</v>
+      </c>
+      <c r="D19" s="13">
+        <v>60</v>
+      </c>
+      <c r="E19" s="13">
+        <v>30</v>
+      </c>
+      <c r="F19" s="13">
+        <v>100</v>
+      </c>
+      <c r="G19" s="13">
+        <v>2</v>
+      </c>
+      <c r="H19" s="13">
+        <v>180</v>
+      </c>
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="14" t="str">
+        <v>710</v>
+      </c>
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14" t="str">
+        <v>730</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.5">
+      <c r="A20" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B20" s="13">
+        <v>320</v>
+      </c>
+      <c r="C20" s="13">
+        <v>50</v>
+      </c>
+      <c r="D20" s="13">
+        <v>40</v>
+      </c>
+      <c r="E20" s="13">
+        <v>30</v>
+      </c>
+      <c r="F20" s="13">
+        <v>300</v>
+      </c>
+      <c r="G20" s="13">
+        <v>6</v>
+      </c>
+      <c r="H20" s="13">
+        <v>60</v>
+      </c>
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J20" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="16"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14" t="str">
+        <v>640</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.5">
+      <c r="A21" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B21" s="13">
+        <v>300</v>
+      </c>
+      <c r="C21" s="13">
+        <v>45</v>
+      </c>
+      <c r="D21" s="13">
+        <v>50</v>
+      </c>
+      <c r="E21" s="13">
+        <v>20</v>
+      </c>
+      <c r="F21" s="13">
+        <v>400</v>
+      </c>
+      <c r="G21" s="13">
+        <v>8</v>
+      </c>
+      <c r="H21" s="13">
+        <v>60</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="14" t="str">
+        <v>875</v>
+      </c>
+      <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="16"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14" t="str">
+        <v>565</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="43.5">
+      <c r="A22" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B22" s="13">
+        <v>320</v>
+      </c>
+      <c r="C22" s="13">
+        <v>30</v>
+      </c>
+      <c r="D22" s="13">
+        <v>45</v>
+      </c>
+      <c r="E22" s="13">
+        <v>30</v>
+      </c>
+      <c r="F22" s="13">
+        <v>250</v>
+      </c>
+      <c r="G22" s="13">
+        <v>5</v>
+      </c>
+      <c r="H22" s="13">
+        <v>60</v>
+      </c>
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="14" t="str">
+        <v>735</v>
+      </c>
+      <c r="J22" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="16"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14" t="str">
+        <v>705</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.5">
+      <c r="A23" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="13">
+        <v>340</v>
+      </c>
+      <c r="C23" s="13">
+        <v>30</v>
+      </c>
+      <c r="D23" s="13">
+        <v>60</v>
+      </c>
+      <c r="E23" s="13">
+        <v>30</v>
+      </c>
+      <c r="F23" s="13">
+        <v>200</v>
+      </c>
+      <c r="G23" s="13">
+        <v>4</v>
+      </c>
+      <c r="H23" s="13">
+        <v>45</v>
+      </c>
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="14" t="str">
+        <v>705</v>
+      </c>
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="16"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14" t="str">
+        <v>735</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15">
+      <c r="A24" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B24" s="13">
+        <v>360</v>
+      </c>
+      <c r="C24" s="13">
+        <v>40</v>
+      </c>
+      <c r="D24" s="13">
+        <v>60</v>
+      </c>
+      <c r="E24" s="13">
+        <v>40</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13">
+        <v>200</v>
+      </c>
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="14" t="str">
+        <v>700</v>
+      </c>
+      <c r="J24" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="16"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14" t="str">
+        <v>740</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15">
+      <c r="A25" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B25" s="13">
+        <v>340</v>
+      </c>
+      <c r="C25" s="13">
+        <v>60</v>
+      </c>
+      <c r="D25" s="13">
+        <v>60</v>
+      </c>
+      <c r="E25" s="13">
+        <v>45</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
+        <v>240</v>
+      </c>
+      <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="str">
+        <v>745</v>
+      </c>
+      <c r="J25" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14" t="str">
+        <v>695</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="43.5">
+      <c r="A26" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B26" s="13">
+        <v>340</v>
+      </c>
+      <c r="C26" s="13">
+        <v>60</v>
+      </c>
+      <c r="D26" s="13">
+        <v>60</v>
+      </c>
+      <c r="E26" s="13">
+        <v>40</v>
+      </c>
+      <c r="F26" s="13">
+        <v>100</v>
+      </c>
+      <c r="G26" s="13">
+        <v>2</v>
+      </c>
+      <c r="H26" s="13">
+        <v>180</v>
+      </c>
+      <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="str">
+        <v>780</v>
+      </c>
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
+        <v>660</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="43.5">
+      <c r="A27" s="8">
+        <v>46266</v>
+      </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1864,10 +2092,14 @@
       <c r="K27" s="15"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
-      <c r="N27" s="16"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
+      <c r="N27" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="43.5">
+      <c r="A28" s="8">
+        <v>46267</v>
+      </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -1886,9 +2118,11 @@
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
-      <c r="N28" s="16"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N28" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="12"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -1910,7 +2144,7 @@
       <c r="M29" s="15"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -1932,7 +2166,7 @@
       <c r="M30" s="15"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14">
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -1954,7 +2188,7 @@
       <c r="M31" s="15"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14">
       <c r="A32" s="12"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -1976,7 +2210,7 @@
       <c r="M32" s="15"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14">
       <c r="A33" s="12"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -1998,7 +2232,7 @@
       <c r="M33" s="15"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14">
       <c r="A34" s="12"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2020,7 +2254,7 @@
       <c r="M34" s="15"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14">
       <c r="A35" s="12"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2042,7 +2276,7 @@
       <c r="M35" s="15"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14">
       <c r="A36" s="12"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -2064,7 +2298,7 @@
       <c r="M36" s="15"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14">
       <c r="A37" s="12"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -2086,7 +2320,7 @@
       <c r="M37" s="15"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14">
       <c r="A38" s="12"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -2108,7 +2342,7 @@
       <c r="M38" s="15"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14">
       <c r="A39" s="12"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -2130,7 +2364,7 @@
       <c r="M39" s="15"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14">
       <c r="A40" s="12"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -2152,7 +2386,7 @@
       <c r="M40" s="15"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14">
       <c r="A41" s="12"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -2174,7 +2408,7 @@
       <c r="M41" s="15"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14">
       <c r="A42" s="12"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -2196,7 +2430,7 @@
       <c r="M42" s="15"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14">
       <c r="A43" s="12"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2218,7 +2452,7 @@
       <c r="M43" s="15"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14">
       <c r="A44" s="12"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -2240,7 +2474,7 @@
       <c r="M44" s="15"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14">
       <c r="A45" s="12"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -2262,7 +2496,7 @@
       <c r="M45" s="15"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14">
       <c r="A46" s="12"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -2284,7 +2518,7 @@
       <c r="M46" s="15"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14">
       <c r="A47" s="12"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -2306,7 +2540,7 @@
       <c r="M47" s="15"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14">
       <c r="A48" s="12"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
@@ -2328,7 +2562,7 @@
       <c r="M48" s="15"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14">
       <c r="A49" s="12"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -2350,7 +2584,7 @@
       <c r="M49" s="15"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14">
       <c r="A50" s="12"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -2372,7 +2606,7 @@
       <c r="M50" s="15"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14">
       <c r="A51" s="12"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -2394,7 +2628,7 @@
       <c r="M51" s="15"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14">
       <c r="A52" s="12"/>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
@@ -2416,7 +2650,7 @@
       <c r="M52" s="15"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14">
       <c r="A53" s="12"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
@@ -2438,7 +2672,7 @@
       <c r="M53" s="15"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14">
       <c r="A54" s="12"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -2460,7 +2694,7 @@
       <c r="M54" s="15"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14">
       <c r="A55" s="12"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -2482,7 +2716,7 @@
       <c r="M55" s="15"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14">
       <c r="A56" s="12"/>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
@@ -2504,7 +2738,7 @@
       <c r="M56" s="15"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14">
       <c r="A57" s="12"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
@@ -2526,7 +2760,7 @@
       <c r="M57" s="15"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14">
       <c r="A58" s="12"/>
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
@@ -2548,7 +2782,7 @@
       <c r="M58" s="15"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14">
       <c r="A59" s="12"/>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
@@ -2570,7 +2804,7 @@
       <c r="M59" s="15"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14">
       <c r="A60" s="12"/>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -2592,7 +2826,7 @@
       <c r="M60" s="15"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14">
       <c r="A61" s="12"/>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>
@@ -2614,7 +2848,7 @@
       <c r="M61" s="15"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14">
       <c r="A62" s="12"/>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -2636,7 +2870,7 @@
       <c r="M62" s="15"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14">
       <c r="A63" s="12"/>
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
@@ -2658,7 +2892,7 @@
       <c r="M63" s="15"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14">
       <c r="A64" s="12"/>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
@@ -2680,7 +2914,7 @@
       <c r="M64" s="15"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14">
       <c r="A65" s="12"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
@@ -2702,7 +2936,7 @@
       <c r="M65" s="15"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14">
       <c r="A66" s="12"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
@@ -2724,7 +2958,7 @@
       <c r="M66" s="15"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14">
       <c r="A67" s="12"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
@@ -2746,7 +2980,7 @@
       <c r="M67" s="15"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14">
       <c r="A68" s="12"/>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
@@ -2768,7 +3002,7 @@
       <c r="M68" s="15"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14">
       <c r="A69" s="12"/>
       <c r="B69" s="13"/>
       <c r="C69" s="13"/>
@@ -2790,7 +3024,7 @@
       <c r="M69" s="15"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14">
       <c r="A70" s="12"/>
       <c r="B70" s="13"/>
       <c r="C70" s="13"/>
@@ -2812,7 +3046,7 @@
       <c r="M70" s="15"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14">
       <c r="A71" s="12"/>
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
@@ -2834,7 +3068,7 @@
       <c r="M71" s="15"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14">
       <c r="A72" s="12"/>
       <c r="B72" s="13"/>
       <c r="C72" s="13"/>
@@ -2856,7 +3090,7 @@
       <c r="M72" s="15"/>
       <c r="N72" s="16"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14">
       <c r="A73" s="12"/>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -2878,7 +3112,7 @@
       <c r="M73" s="15"/>
       <c r="N73" s="16"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14">
       <c r="A74" s="12"/>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
@@ -2900,7 +3134,7 @@
       <c r="M74" s="15"/>
       <c r="N74" s="16"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14">
       <c r="A75" s="12"/>
       <c r="B75" s="13"/>
       <c r="C75" s="13"/>
@@ -2922,7 +3156,7 @@
       <c r="M75" s="15"/>
       <c r="N75" s="16"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14">
       <c r="A76" s="12"/>
       <c r="B76" s="13"/>
       <c r="C76" s="13"/>
@@ -2944,7 +3178,7 @@
       <c r="M76" s="15"/>
       <c r="N76" s="16"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14">
       <c r="A77" s="12"/>
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
@@ -2966,7 +3200,7 @@
       <c r="M77" s="15"/>
       <c r="N77" s="16"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14">
       <c r="A78" s="12"/>
       <c r="B78" s="13"/>
       <c r="C78" s="13"/>
@@ -2988,7 +3222,7 @@
       <c r="M78" s="15"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14">
       <c r="A79" s="12"/>
       <c r="B79" s="13"/>
       <c r="C79" s="13"/>
@@ -3010,7 +3244,7 @@
       <c r="M79" s="15"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14">
       <c r="A80" s="12"/>
       <c r="B80" s="13"/>
       <c r="C80" s="13"/>
@@ -3032,7 +3266,7 @@
       <c r="M80" s="15"/>
       <c r="N80" s="16"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14">
       <c r="A81" s="12"/>
       <c r="B81" s="13"/>
       <c r="C81" s="13"/>
@@ -3054,7 +3288,7 @@
       <c r="M81" s="15"/>
       <c r="N81" s="16"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14">
       <c r="A82" s="12"/>
       <c r="B82" s="13"/>
       <c r="C82" s="13"/>
@@ -3076,7 +3310,7 @@
       <c r="M82" s="15"/>
       <c r="N82" s="16"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14">
       <c r="A83" s="12"/>
       <c r="B83" s="13"/>
       <c r="C83" s="13"/>
@@ -3098,7 +3332,7 @@
       <c r="M83" s="15"/>
       <c r="N83" s="16"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14">
       <c r="A84" s="12"/>
       <c r="B84" s="13"/>
       <c r="C84" s="13"/>
@@ -3120,7 +3354,7 @@
       <c r="M84" s="15"/>
       <c r="N84" s="16"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14">
       <c r="A85" s="12"/>
       <c r="B85" s="13"/>
       <c r="C85" s="13"/>
@@ -3142,7 +3376,7 @@
       <c r="M85" s="15"/>
       <c r="N85" s="16"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14">
       <c r="A86" s="12"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -3164,7 +3398,7 @@
       <c r="M86" s="15"/>
       <c r="N86" s="16"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14">
       <c r="A87" s="12"/>
       <c r="B87" s="13"/>
       <c r="C87" s="13"/>
@@ -3186,7 +3420,7 @@
       <c r="M87" s="15"/>
       <c r="N87" s="16"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14">
       <c r="A88" s="12"/>
       <c r="B88" s="13"/>
       <c r="C88" s="13"/>
@@ -3208,7 +3442,7 @@
       <c r="M88" s="15"/>
       <c r="N88" s="16"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14">
       <c r="A89" s="12"/>
       <c r="B89" s="13"/>
       <c r="C89" s="13"/>
@@ -3230,7 +3464,7 @@
       <c r="M89" s="15"/>
       <c r="N89" s="16"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14">
       <c r="A90" s="12"/>
       <c r="B90" s="13"/>
       <c r="C90" s="13"/>
@@ -3252,7 +3486,7 @@
       <c r="M90" s="15"/>
       <c r="N90" s="16"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14">
       <c r="A91" s="12"/>
       <c r="B91" s="13"/>
       <c r="C91" s="13"/>
@@ -3274,7 +3508,7 @@
       <c r="M91" s="15"/>
       <c r="N91" s="16"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14">
       <c r="A92" s="12"/>
       <c r="B92" s="13"/>
       <c r="C92" s="13"/>
@@ -3296,7 +3530,7 @@
       <c r="M92" s="15"/>
       <c r="N92" s="16"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14">
       <c r="A93" s="12"/>
       <c r="B93" s="13"/>
       <c r="C93" s="13"/>
@@ -3318,7 +3552,7 @@
       <c r="M93" s="15"/>
       <c r="N93" s="16"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14">
       <c r="A94" s="12"/>
       <c r="B94" s="13"/>
       <c r="C94" s="13"/>
@@ -3340,7 +3574,7 @@
       <c r="M94" s="15"/>
       <c r="N94" s="16"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14">
       <c r="A95" s="12"/>
       <c r="B95" s="13"/>
       <c r="C95" s="13"/>
@@ -3362,7 +3596,7 @@
       <c r="M95" s="15"/>
       <c r="N95" s="16"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14">
       <c r="A96" s="12"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
@@ -3384,7 +3618,7 @@
       <c r="M96" s="15"/>
       <c r="N96" s="16"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14">
       <c r="A97" s="12"/>
       <c r="B97" s="13"/>
       <c r="C97" s="13"/>
@@ -3406,7 +3640,7 @@
       <c r="M97" s="15"/>
       <c r="N97" s="16"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14">
       <c r="A98" s="12"/>
       <c r="B98" s="13"/>
       <c r="C98" s="13"/>
@@ -3428,7 +3662,7 @@
       <c r="M98" s="15"/>
       <c r="N98" s="16"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14">
       <c r="A99" s="12"/>
       <c r="B99" s="13"/>
       <c r="C99" s="13"/>
@@ -3450,7 +3684,7 @@
       <c r="M99" s="15"/>
       <c r="N99" s="16"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14">
       <c r="A100" s="12"/>
       <c r="B100" s="13"/>
       <c r="C100" s="13"/>
@@ -3472,7 +3706,7 @@
       <c r="M100" s="15"/>
       <c r="N100" s="16"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14">
       <c r="A101" s="12"/>
       <c r="B101" s="13"/>
       <c r="C101" s="13"/>
@@ -3494,7 +3728,7 @@
       <c r="M101" s="15"/>
       <c r="N101" s="16"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14">
       <c r="A102" s="12"/>
       <c r="B102" s="13"/>
       <c r="C102" s="13"/>
@@ -3516,7 +3750,7 @@
       <c r="M102" s="15"/>
       <c r="N102" s="16"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14">
       <c r="A103" s="12"/>
       <c r="B103" s="13"/>
       <c r="C103" s="13"/>
@@ -3538,7 +3772,7 @@
       <c r="M103" s="15"/>
       <c r="N103" s="16"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14">
       <c r="A104" s="12"/>
       <c r="B104" s="13"/>
       <c r="C104" s="13"/>
@@ -3560,7 +3794,7 @@
       <c r="M104" s="15"/>
       <c r="N104" s="16"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14">
       <c r="A105" s="12"/>
       <c r="B105" s="13"/>
       <c r="C105" s="13"/>
@@ -3582,7 +3816,7 @@
       <c r="M105" s="15"/>
       <c r="N105" s="16"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14">
       <c r="A106" s="12"/>
       <c r="B106" s="13"/>
       <c r="C106" s="13"/>
@@ -3604,7 +3838,7 @@
       <c r="M106" s="15"/>
       <c r="N106" s="16"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14">
       <c r="A107" s="12"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
@@ -3626,7 +3860,7 @@
       <c r="M107" s="15"/>
       <c r="N107" s="16"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14">
       <c r="A108" s="12"/>
       <c r="B108" s="13"/>
       <c r="C108" s="13"/>
@@ -3648,7 +3882,7 @@
       <c r="M108" s="15"/>
       <c r="N108" s="16"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14">
       <c r="A109" s="12"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13"/>
@@ -3670,7 +3904,7 @@
       <c r="M109" s="15"/>
       <c r="N109" s="16"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14">
       <c r="A110" s="12"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13"/>
@@ -3692,7 +3926,7 @@
       <c r="M110" s="15"/>
       <c r="N110" s="16"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14">
       <c r="A111" s="12"/>
       <c r="B111" s="13"/>
       <c r="C111" s="13"/>
@@ -3714,7 +3948,7 @@
       <c r="M111" s="15"/>
       <c r="N111" s="16"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14">
       <c r="A112" s="12"/>
       <c r="B112" s="13"/>
       <c r="C112" s="13"/>
@@ -3736,7 +3970,7 @@
       <c r="M112" s="15"/>
       <c r="N112" s="16"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14">
       <c r="A113" s="12"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13"/>
@@ -3758,7 +3992,7 @@
       <c r="M113" s="15"/>
       <c r="N113" s="16"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14">
       <c r="A114" s="12"/>
       <c r="B114" s="13"/>
       <c r="C114" s="13"/>
@@ -3780,7 +4014,7 @@
       <c r="M114" s="15"/>
       <c r="N114" s="16"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14">
       <c r="A115" s="12"/>
       <c r="B115" s="13"/>
       <c r="C115" s="13"/>
@@ -3802,7 +4036,7 @@
       <c r="M115" s="15"/>
       <c r="N115" s="16"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14">
       <c r="A116" s="12"/>
       <c r="B116" s="13"/>
       <c r="C116" s="13"/>
@@ -3824,7 +4058,7 @@
       <c r="M116" s="15"/>
       <c r="N116" s="16"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14">
       <c r="A117" s="12"/>
       <c r="B117" s="13"/>
       <c r="C117" s="13"/>
@@ -3846,7 +4080,7 @@
       <c r="M117" s="15"/>
       <c r="N117" s="16"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14">
       <c r="A118" s="12"/>
       <c r="B118" s="13"/>
       <c r="C118" s="13"/>
@@ -3868,7 +4102,7 @@
       <c r="M118" s="15"/>
       <c r="N118" s="16"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14">
       <c r="A119" s="12"/>
       <c r="B119" s="13"/>
       <c r="C119" s="13"/>
@@ -3890,7 +4124,7 @@
       <c r="M119" s="15"/>
       <c r="N119" s="16"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14">
       <c r="A120" s="12"/>
       <c r="B120" s="13"/>
       <c r="C120" s="13"/>
@@ -3912,7 +4146,7 @@
       <c r="M120" s="15"/>
       <c r="N120" s="16"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14">
       <c r="A121" s="12"/>
       <c r="B121" s="13"/>
       <c r="C121" s="13"/>
@@ -3934,7 +4168,7 @@
       <c r="M121" s="15"/>
       <c r="N121" s="16"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14">
       <c r="A122" s="12"/>
       <c r="B122" s="13"/>
       <c r="C122" s="13"/>
@@ -3956,7 +4190,7 @@
       <c r="M122" s="15"/>
       <c r="N122" s="16"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14">
       <c r="A123" s="12"/>
       <c r="B123" s="13"/>
       <c r="C123" s="13"/>
@@ -3978,7 +4212,7 @@
       <c r="M123" s="15"/>
       <c r="N123" s="16"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14">
       <c r="A124" s="12"/>
       <c r="B124" s="13"/>
       <c r="C124" s="13"/>
@@ -4000,7 +4234,7 @@
       <c r="M124" s="15"/>
       <c r="N124" s="16"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14">
       <c r="A125" s="12"/>
       <c r="B125" s="13"/>
       <c r="C125" s="13"/>
@@ -4022,7 +4256,7 @@
       <c r="M125" s="15"/>
       <c r="N125" s="16"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14">
       <c r="A126" s="12"/>
       <c r="B126" s="13"/>
       <c r="C126" s="13"/>
@@ -4044,7 +4278,7 @@
       <c r="M126" s="15"/>
       <c r="N126" s="16"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14">
       <c r="A127" s="12"/>
       <c r="B127" s="13"/>
       <c r="C127" s="13"/>
@@ -4066,7 +4300,7 @@
       <c r="M127" s="15"/>
       <c r="N127" s="16"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14">
       <c r="A128" s="12"/>
       <c r="B128" s="13"/>
       <c r="C128" s="13"/>
@@ -4088,7 +4322,7 @@
       <c r="M128" s="15"/>
       <c r="N128" s="16"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14">
       <c r="A129" s="12"/>
       <c r="B129" s="13"/>
       <c r="C129" s="13"/>
@@ -4110,7 +4344,7 @@
       <c r="M129" s="15"/>
       <c r="N129" s="16"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14">
       <c r="A130" s="12"/>
       <c r="B130" s="13"/>
       <c r="C130" s="13"/>
@@ -4132,7 +4366,7 @@
       <c r="M130" s="15"/>
       <c r="N130" s="16"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14">
       <c r="A131" s="12"/>
       <c r="B131" s="13"/>
       <c r="C131" s="13"/>
@@ -4154,7 +4388,7 @@
       <c r="M131" s="15"/>
       <c r="N131" s="16"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14">
       <c r="A132" s="12"/>
       <c r="B132" s="13"/>
       <c r="C132" s="13"/>
@@ -4176,7 +4410,7 @@
       <c r="M132" s="15"/>
       <c r="N132" s="16"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14">
       <c r="A133" s="12"/>
       <c r="B133" s="13"/>
       <c r="C133" s="13"/>
@@ -4198,7 +4432,7 @@
       <c r="M133" s="15"/>
       <c r="N133" s="16"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14">
       <c r="A134" s="12"/>
       <c r="B134" s="13"/>
       <c r="C134" s="13"/>
@@ -4220,7 +4454,7 @@
       <c r="M134" s="15"/>
       <c r="N134" s="16"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14">
       <c r="A135" s="12"/>
       <c r="B135" s="13"/>
       <c r="C135" s="13"/>
@@ -4242,7 +4476,7 @@
       <c r="M135" s="15"/>
       <c r="N135" s="16"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14">
       <c r="A136" s="12"/>
       <c r="B136" s="13"/>
       <c r="C136" s="13"/>
@@ -4264,7 +4498,7 @@
       <c r="M136" s="15"/>
       <c r="N136" s="16"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14">
       <c r="A137" s="12"/>
       <c r="B137" s="13"/>
       <c r="C137" s="13"/>
@@ -4286,7 +4520,7 @@
       <c r="M137" s="15"/>
       <c r="N137" s="16"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14">
       <c r="A138" s="12"/>
       <c r="B138" s="13"/>
       <c r="C138" s="13"/>
@@ -4308,7 +4542,7 @@
       <c r="M138" s="15"/>
       <c r="N138" s="16"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14">
       <c r="A139" s="12"/>
       <c r="B139" s="13"/>
       <c r="C139" s="13"/>
@@ -4330,7 +4564,7 @@
       <c r="M139" s="15"/>
       <c r="N139" s="16"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14">
       <c r="A140" s="12"/>
       <c r="B140" s="13"/>
       <c r="C140" s="13"/>
@@ -4352,7 +4586,7 @@
       <c r="M140" s="15"/>
       <c r="N140" s="16"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14">
       <c r="A141" s="12"/>
       <c r="B141" s="13"/>
       <c r="C141" s="13"/>
@@ -4374,7 +4608,7 @@
       <c r="M141" s="15"/>
       <c r="N141" s="16"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14">
       <c r="A142" s="12"/>
       <c r="B142" s="13"/>
       <c r="C142" s="13"/>
@@ -4396,7 +4630,7 @@
       <c r="M142" s="15"/>
       <c r="N142" s="16"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14">
       <c r="A143" s="12"/>
       <c r="B143" s="13"/>
       <c r="C143" s="13"/>
@@ -4418,7 +4652,7 @@
       <c r="M143" s="15"/>
       <c r="N143" s="16"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14">
       <c r="A144" s="12"/>
       <c r="B144" s="13"/>
       <c r="C144" s="13"/>
@@ -4440,7 +4674,7 @@
       <c r="M144" s="15"/>
       <c r="N144" s="16"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14">
       <c r="A145" s="12"/>
       <c r="B145" s="13"/>
       <c r="C145" s="13"/>
@@ -4462,7 +4696,7 @@
       <c r="M145" s="15"/>
       <c r="N145" s="16"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14">
       <c r="A146" s="12"/>
       <c r="B146" s="13"/>
       <c r="C146" s="13"/>
@@ -4484,7 +4718,7 @@
       <c r="M146" s="15"/>
       <c r="N146" s="16"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14">
       <c r="A147" s="12"/>
       <c r="B147" s="13"/>
       <c r="C147" s="13"/>
@@ -4506,7 +4740,7 @@
       <c r="M147" s="15"/>
       <c r="N147" s="16"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14">
       <c r="A148" s="12"/>
       <c r="B148" s="13"/>
       <c r="C148" s="13"/>
@@ -4528,7 +4762,7 @@
       <c r="M148" s="15"/>
       <c r="N148" s="16"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14">
       <c r="A149" s="12"/>
       <c r="B149" s="13"/>
       <c r="C149" s="13"/>
@@ -4550,7 +4784,7 @@
       <c r="M149" s="15"/>
       <c r="N149" s="16"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14">
       <c r="A150" s="12"/>
       <c r="B150" s="13"/>
       <c r="C150" s="13"/>
@@ -4572,7 +4806,7 @@
       <c r="M150" s="15"/>
       <c r="N150" s="16"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14">
       <c r="A151" s="12"/>
       <c r="B151" s="13"/>
       <c r="C151" s="13"/>
@@ -4594,7 +4828,7 @@
       <c r="M151" s="15"/>
       <c r="N151" s="16"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14">
       <c r="A152" s="12"/>
       <c r="B152" s="13"/>
       <c r="C152" s="13"/>
@@ -4616,7 +4850,7 @@
       <c r="M152" s="15"/>
       <c r="N152" s="16"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14">
       <c r="A153" s="12"/>
       <c r="B153" s="13"/>
       <c r="C153" s="13"/>
@@ -4638,7 +4872,7 @@
       <c r="M153" s="15"/>
       <c r="N153" s="16"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14">
       <c r="A154" s="12"/>
       <c r="B154" s="13"/>
       <c r="C154" s="13"/>
@@ -4660,7 +4894,7 @@
       <c r="M154" s="15"/>
       <c r="N154" s="16"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14">
       <c r="A155" s="12"/>
       <c r="B155" s="13"/>
       <c r="C155" s="13"/>
@@ -4682,7 +4916,7 @@
       <c r="M155" s="15"/>
       <c r="N155" s="16"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14">
       <c r="A156" s="12"/>
       <c r="B156" s="13"/>
       <c r="C156" s="13"/>
@@ -4704,7 +4938,7 @@
       <c r="M156" s="15"/>
       <c r="N156" s="16"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14">
       <c r="A157" s="12"/>
       <c r="B157" s="13"/>
       <c r="C157" s="13"/>
@@ -4726,7 +4960,7 @@
       <c r="M157" s="15"/>
       <c r="N157" s="16"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14">
       <c r="A158" s="12"/>
       <c r="B158" s="13"/>
       <c r="C158" s="13"/>
@@ -4748,7 +4982,7 @@
       <c r="M158" s="15"/>
       <c r="N158" s="16"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14">
       <c r="A159" s="12"/>
       <c r="B159" s="13"/>
       <c r="C159" s="13"/>
@@ -4770,7 +5004,7 @@
       <c r="M159" s="15"/>
       <c r="N159" s="16"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14">
       <c r="A160" s="12"/>
       <c r="B160" s="13"/>
       <c r="C160" s="13"/>
@@ -4792,7 +5026,7 @@
       <c r="M160" s="15"/>
       <c r="N160" s="16"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14">
       <c r="A161" s="12"/>
       <c r="B161" s="13"/>
       <c r="C161" s="13"/>
@@ -4814,7 +5048,7 @@
       <c r="M161" s="15"/>
       <c r="N161" s="16"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14">
       <c r="A162" s="12"/>
       <c r="B162" s="13"/>
       <c r="C162" s="13"/>
@@ -4836,7 +5070,7 @@
       <c r="M162" s="15"/>
       <c r="N162" s="16"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14">
       <c r="A163" s="12"/>
       <c r="B163" s="13"/>
       <c r="C163" s="13"/>
@@ -4858,7 +5092,7 @@
       <c r="M163" s="15"/>
       <c r="N163" s="16"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14">
       <c r="A164" s="12"/>
       <c r="B164" s="13"/>
       <c r="C164" s="13"/>
@@ -4880,7 +5114,7 @@
       <c r="M164" s="15"/>
       <c r="N164" s="16"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14">
       <c r="A165" s="12"/>
       <c r="B165" s="13"/>
       <c r="C165" s="13"/>
@@ -4902,7 +5136,7 @@
       <c r="M165" s="15"/>
       <c r="N165" s="16"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14">
       <c r="A166" s="12"/>
       <c r="B166" s="13"/>
       <c r="C166" s="13"/>
@@ -4924,7 +5158,7 @@
       <c r="M166" s="15"/>
       <c r="N166" s="16"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14">
       <c r="A167" s="12"/>
       <c r="B167" s="13"/>
       <c r="C167" s="13"/>
@@ -4946,7 +5180,7 @@
       <c r="M167" s="15"/>
       <c r="N167" s="16"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14">
       <c r="A168" s="12"/>
       <c r="B168" s="13"/>
       <c r="C168" s="13"/>
@@ -4968,7 +5202,7 @@
       <c r="M168" s="15"/>
       <c r="N168" s="16"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14">
       <c r="A169" s="12"/>
       <c r="B169" s="13"/>
       <c r="C169" s="13"/>
@@ -4990,7 +5224,7 @@
       <c r="M169" s="15"/>
       <c r="N169" s="16"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14">
       <c r="A170" s="12"/>
       <c r="B170" s="13"/>
       <c r="C170" s="13"/>
@@ -5012,7 +5246,7 @@
       <c r="M170" s="15"/>
       <c r="N170" s="16"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14">
       <c r="A171" s="12"/>
       <c r="B171" s="13"/>
       <c r="C171" s="13"/>
@@ -5034,7 +5268,7 @@
       <c r="M171" s="15"/>
       <c r="N171" s="16"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14">
       <c r="A172" s="12"/>
       <c r="B172" s="13"/>
       <c r="C172" s="13"/>
@@ -5056,7 +5290,7 @@
       <c r="M172" s="15"/>
       <c r="N172" s="16"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14">
       <c r="A173" s="12"/>
       <c r="B173" s="13"/>
       <c r="C173" s="13"/>
@@ -5078,7 +5312,7 @@
       <c r="M173" s="15"/>
       <c r="N173" s="16"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14">
       <c r="A174" s="12"/>
       <c r="B174" s="13"/>
       <c r="C174" s="13"/>
@@ -5100,7 +5334,7 @@
       <c r="M174" s="15"/>
       <c r="N174" s="16"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14">
       <c r="A175" s="12"/>
       <c r="B175" s="13"/>
       <c r="C175" s="13"/>
@@ -5122,7 +5356,7 @@
       <c r="M175" s="15"/>
       <c r="N175" s="16"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14">
       <c r="A176" s="12"/>
       <c r="B176" s="13"/>
       <c r="C176" s="13"/>
@@ -5144,7 +5378,7 @@
       <c r="M176" s="15"/>
       <c r="N176" s="16"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14">
       <c r="A177" s="12"/>
       <c r="B177" s="13"/>
       <c r="C177" s="13"/>
@@ -5166,7 +5400,7 @@
       <c r="M177" s="15"/>
       <c r="N177" s="16"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14">
       <c r="A178" s="12"/>
       <c r="B178" s="13"/>
       <c r="C178" s="13"/>
@@ -5188,7 +5422,7 @@
       <c r="M178" s="15"/>
       <c r="N178" s="16"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14">
       <c r="A179" s="12"/>
       <c r="B179" s="13"/>
       <c r="C179" s="13"/>
@@ -5210,7 +5444,7 @@
       <c r="M179" s="15"/>
       <c r="N179" s="16"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14">
       <c r="A180" s="12"/>
       <c r="B180" s="13"/>
       <c r="C180" s="13"/>
@@ -5232,7 +5466,7 @@
       <c r="M180" s="15"/>
       <c r="N180" s="16"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14">
       <c r="A181" s="12"/>
       <c r="B181" s="13"/>
       <c r="C181" s="13"/>
@@ -5254,7 +5488,7 @@
       <c r="M181" s="15"/>
       <c r="N181" s="16"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14">
       <c r="A182" s="12"/>
       <c r="B182" s="13"/>
       <c r="C182" s="13"/>
@@ -5276,7 +5510,7 @@
       <c r="M182" s="15"/>
       <c r="N182" s="16"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14">
       <c r="A183" s="12"/>
       <c r="B183" s="13"/>
       <c r="C183" s="13"/>
@@ -5298,7 +5532,7 @@
       <c r="M183" s="15"/>
       <c r="N183" s="16"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14">
       <c r="A184" s="12"/>
       <c r="B184" s="13"/>
       <c r="C184" s="13"/>
@@ -5320,7 +5554,7 @@
       <c r="M184" s="15"/>
       <c r="N184" s="16"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14">
       <c r="A185" s="12"/>
       <c r="B185" s="13"/>
       <c r="C185" s="13"/>
@@ -5342,7 +5576,7 @@
       <c r="M185" s="15"/>
       <c r="N185" s="16"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14">
       <c r="A186" s="12"/>
       <c r="B186" s="13"/>
       <c r="C186" s="13"/>
@@ -5364,7 +5598,7 @@
       <c r="M186" s="15"/>
       <c r="N186" s="16"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14">
       <c r="A187" s="12"/>
       <c r="B187" s="13"/>
       <c r="C187" s="13"/>
@@ -5386,7 +5620,7 @@
       <c r="M187" s="15"/>
       <c r="N187" s="16"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14">
       <c r="A188" s="12"/>
       <c r="B188" s="13"/>
       <c r="C188" s="13"/>
@@ -5408,7 +5642,7 @@
       <c r="M188" s="15"/>
       <c r="N188" s="16"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14">
       <c r="A189" s="12"/>
       <c r="B189" s="13"/>
       <c r="C189" s="13"/>
@@ -5430,7 +5664,7 @@
       <c r="M189" s="15"/>
       <c r="N189" s="16"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14">
       <c r="A190" s="12"/>
       <c r="B190" s="13"/>
       <c r="C190" s="13"/>
@@ -5452,7 +5686,7 @@
       <c r="M190" s="15"/>
       <c r="N190" s="16"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14">
       <c r="A191" s="12"/>
       <c r="B191" s="13"/>
       <c r="C191" s="13"/>
@@ -5474,7 +5708,7 @@
       <c r="M191" s="15"/>
       <c r="N191" s="16"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14">
       <c r="A192" s="12"/>
       <c r="B192" s="13"/>
       <c r="C192" s="13"/>
@@ -5496,7 +5730,7 @@
       <c r="M192" s="15"/>
       <c r="N192" s="16"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14">
       <c r="A193" s="12"/>
       <c r="B193" s="13"/>
       <c r="C193" s="13"/>
@@ -5518,7 +5752,7 @@
       <c r="M193" s="15"/>
       <c r="N193" s="16"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14">
       <c r="A194" s="12"/>
       <c r="B194" s="13"/>
       <c r="C194" s="13"/>
@@ -5540,7 +5774,7 @@
       <c r="M194" s="15"/>
       <c r="N194" s="16"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14">
       <c r="A195" s="12"/>
       <c r="B195" s="13"/>
       <c r="C195" s="13"/>
@@ -5562,7 +5796,7 @@
       <c r="M195" s="15"/>
       <c r="N195" s="16"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14">
       <c r="A196" s="12"/>
       <c r="B196" s="13"/>
       <c r="C196" s="13"/>
@@ -5584,7 +5818,7 @@
       <c r="M196" s="15"/>
       <c r="N196" s="16"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14">
       <c r="A197" s="12"/>
       <c r="B197" s="13"/>
       <c r="C197" s="13"/>
@@ -5606,7 +5840,7 @@
       <c r="M197" s="15"/>
       <c r="N197" s="16"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14">
       <c r="A198" s="12"/>
       <c r="B198" s="13"/>
       <c r="C198" s="13"/>
@@ -5628,7 +5862,7 @@
       <c r="M198" s="15"/>
       <c r="N198" s="16"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14">
       <c r="A199" s="12"/>
       <c r="B199" s="13"/>
       <c r="C199" s="13"/>
@@ -5650,7 +5884,7 @@
       <c r="M199" s="15"/>
       <c r="N199" s="16"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14">
       <c r="A200" s="12"/>
       <c r="B200" s="13"/>
       <c r="C200" s="13"/>
@@ -5672,7 +5906,7 @@
       <c r="M200" s="15"/>
       <c r="N200" s="16"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14">
       <c r="A201" s="12"/>
       <c r="B201" s="13"/>
       <c r="C201" s="13"/>
@@ -5694,7 +5928,7 @@
       <c r="M201" s="15"/>
       <c r="N201" s="16"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14">
       <c r="A202" s="12"/>
       <c r="B202" s="13"/>
       <c r="C202" s="13"/>
@@ -5716,7 +5950,7 @@
       <c r="M202" s="15"/>
       <c r="N202" s="16"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14">
       <c r="A203" s="12"/>
       <c r="B203" s="13"/>
       <c r="C203" s="13"/>
@@ -5738,7 +5972,7 @@
       <c r="M203" s="15"/>
       <c r="N203" s="16"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14">
       <c r="A204" s="12"/>
       <c r="B204" s="13"/>
       <c r="C204" s="13"/>
@@ -5760,7 +5994,7 @@
       <c r="M204" s="15"/>
       <c r="N204" s="16"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14">
       <c r="A205" s="12"/>
       <c r="B205" s="13"/>
       <c r="C205" s="13"/>
@@ -5782,7 +6016,7 @@
       <c r="M205" s="15"/>
       <c r="N205" s="16"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14">
       <c r="A206" s="12"/>
       <c r="B206" s="13"/>
       <c r="C206" s="13"/>
@@ -5804,7 +6038,7 @@
       <c r="M206" s="15"/>
       <c r="N206" s="16"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14">
       <c r="A207" s="12"/>
       <c r="B207" s="13"/>
       <c r="C207" s="13"/>
@@ -5826,7 +6060,7 @@
       <c r="M207" s="15"/>
       <c r="N207" s="16"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14">
       <c r="A208" s="12"/>
       <c r="B208" s="13"/>
       <c r="C208" s="13"/>
@@ -5848,7 +6082,7 @@
       <c r="M208" s="15"/>
       <c r="N208" s="16"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14">
       <c r="A209" s="12"/>
       <c r="B209" s="13"/>
       <c r="C209" s="13"/>
@@ -5870,7 +6104,7 @@
       <c r="M209" s="15"/>
       <c r="N209" s="16"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14">
       <c r="A210" s="12"/>
       <c r="B210" s="13"/>
       <c r="C210" s="13"/>
@@ -5892,7 +6126,7 @@
       <c r="M210" s="15"/>
       <c r="N210" s="16"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14">
       <c r="A211" s="12"/>
       <c r="B211" s="13"/>
       <c r="C211" s="13"/>
@@ -5914,7 +6148,7 @@
       <c r="M211" s="15"/>
       <c r="N211" s="16"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14">
       <c r="A212" s="12"/>
       <c r="B212" s="13"/>
       <c r="C212" s="13"/>
@@ -5936,7 +6170,7 @@
       <c r="M212" s="15"/>
       <c r="N212" s="16"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14">
       <c r="A213" s="12"/>
       <c r="B213" s="13"/>
       <c r="C213" s="13"/>
@@ -5958,7 +6192,7 @@
       <c r="M213" s="15"/>
       <c r="N213" s="16"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14">
       <c r="A214" s="12"/>
       <c r="B214" s="13"/>
       <c r="C214" s="13"/>
@@ -5980,7 +6214,7 @@
       <c r="M214" s="15"/>
       <c r="N214" s="16"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14">
       <c r="A215" s="12"/>
       <c r="B215" s="13"/>
       <c r="C215" s="13"/>
@@ -6002,7 +6236,7 @@
       <c r="M215" s="15"/>
       <c r="N215" s="16"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14">
       <c r="A216" s="12"/>
       <c r="B216" s="13"/>
       <c r="C216" s="13"/>
@@ -6024,7 +6258,7 @@
       <c r="M216" s="15"/>
       <c r="N216" s="16"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14">
       <c r="A217" s="12"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13"/>
@@ -6046,7 +6280,7 @@
       <c r="M217" s="15"/>
       <c r="N217" s="16"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14">
       <c r="A218" s="12"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13"/>
@@ -6068,7 +6302,7 @@
       <c r="M218" s="15"/>
       <c r="N218" s="16"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14">
       <c r="A219" s="12"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13"/>
@@ -6090,7 +6324,7 @@
       <c r="M219" s="15"/>
       <c r="N219" s="16"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14">
       <c r="A220" s="12"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13"/>
@@ -6112,7 +6346,7 @@
       <c r="M220" s="15"/>
       <c r="N220" s="16"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14">
       <c r="A221" s="12"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13"/>
@@ -6134,7 +6368,7 @@
       <c r="M221" s="15"/>
       <c r="N221" s="16"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14">
       <c r="A222" s="12"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13"/>
@@ -6156,7 +6390,7 @@
       <c r="M222" s="15"/>
       <c r="N222" s="16"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14">
       <c r="A223" s="12"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13"/>
@@ -6178,7 +6412,7 @@
       <c r="M223" s="15"/>
       <c r="N223" s="16"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14">
       <c r="A224" s="12"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
@@ -6200,7 +6434,7 @@
       <c r="M224" s="15"/>
       <c r="N224" s="16"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14">
       <c r="A225" s="12"/>
       <c r="B225" s="13"/>
       <c r="C225" s="13"/>
@@ -6222,7 +6456,7 @@
       <c r="M225" s="15"/>
       <c r="N225" s="16"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14">
       <c r="A226" s="12"/>
       <c r="B226" s="13"/>
       <c r="C226" s="13"/>
@@ -6244,7 +6478,7 @@
       <c r="M226" s="15"/>
       <c r="N226" s="16"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14">
       <c r="A227" s="12"/>
       <c r="B227" s="13"/>
       <c r="C227" s="13"/>
@@ -6266,7 +6500,7 @@
       <c r="M227" s="15"/>
       <c r="N227" s="16"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14">
       <c r="A228" s="12"/>
       <c r="B228" s="13"/>
       <c r="C228" s="13"/>
@@ -6288,7 +6522,7 @@
       <c r="M228" s="15"/>
       <c r="N228" s="16"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14">
       <c r="A229" s="12"/>
       <c r="B229" s="13"/>
       <c r="C229" s="13"/>
@@ -6310,7 +6544,7 @@
       <c r="M229" s="15"/>
       <c r="N229" s="16"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14">
       <c r="A230" s="12"/>
       <c r="B230" s="13"/>
       <c r="C230" s="13"/>
@@ -6332,7 +6566,7 @@
       <c r="M230" s="15"/>
       <c r="N230" s="16"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14">
       <c r="A231" s="12"/>
       <c r="B231" s="13"/>
       <c r="C231" s="13"/>
@@ -6354,7 +6588,7 @@
       <c r="M231" s="15"/>
       <c r="N231" s="16"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14">
       <c r="A232" s="12"/>
       <c r="B232" s="13"/>
       <c r="C232" s="13"/>
@@ -6376,7 +6610,7 @@
       <c r="M232" s="15"/>
       <c r="N232" s="16"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14">
       <c r="A233" s="12"/>
       <c r="B233" s="13"/>
       <c r="C233" s="13"/>
@@ -6398,7 +6632,7 @@
       <c r="M233" s="15"/>
       <c r="N233" s="16"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14">
       <c r="A234" s="12"/>
       <c r="B234" s="13"/>
       <c r="C234" s="13"/>
@@ -6420,7 +6654,7 @@
       <c r="M234" s="15"/>
       <c r="N234" s="16"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14">
       <c r="A235" s="12"/>
       <c r="B235" s="13"/>
       <c r="C235" s="13"/>
@@ -6442,7 +6676,7 @@
       <c r="M235" s="15"/>
       <c r="N235" s="16"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14">
       <c r="A236" s="12"/>
       <c r="B236" s="13"/>
       <c r="C236" s="13"/>
@@ -6464,7 +6698,7 @@
       <c r="M236" s="15"/>
       <c r="N236" s="16"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14">
       <c r="A237" s="12"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13"/>
@@ -6486,7 +6720,7 @@
       <c r="M237" s="15"/>
       <c r="N237" s="16"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:14">
       <c r="A238" s="12"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13"/>
@@ -6508,7 +6742,7 @@
       <c r="M238" s="15"/>
       <c r="N238" s="16"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14">
       <c r="A239" s="12"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13"/>
@@ -6530,7 +6764,7 @@
       <c r="M239" s="15"/>
       <c r="N239" s="16"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14">
       <c r="A240" s="12"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13"/>
@@ -6552,7 +6786,7 @@
       <c r="M240" s="15"/>
       <c r="N240" s="16"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14">
       <c r="A241" s="12"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13"/>
@@ -6574,7 +6808,7 @@
       <c r="M241" s="15"/>
       <c r="N241" s="16"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14">
       <c r="A242" s="12"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13"/>
@@ -6596,7 +6830,7 @@
       <c r="M242" s="15"/>
       <c r="N242" s="16"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14">
       <c r="A243" s="12"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13"/>
@@ -6618,7 +6852,7 @@
       <c r="M243" s="15"/>
       <c r="N243" s="16"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14">
       <c r="A244" s="12"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13"/>
@@ -6640,7 +6874,7 @@
       <c r="M244" s="15"/>
       <c r="N244" s="16"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14">
       <c r="A245" s="12"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
@@ -6662,7 +6896,7 @@
       <c r="M245" s="15"/>
       <c r="N245" s="16"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14">
       <c r="A246" s="12"/>
       <c r="B246" s="13"/>
       <c r="C246" s="13"/>
@@ -6684,7 +6918,7 @@
       <c r="M246" s="15"/>
       <c r="N246" s="16"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14">
       <c r="A247" s="12"/>
       <c r="B247" s="13"/>
       <c r="C247" s="13"/>
@@ -6706,7 +6940,7 @@
       <c r="M247" s="15"/>
       <c r="N247" s="16"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14">
       <c r="A248" s="12"/>
       <c r="B248" s="13"/>
       <c r="C248" s="13"/>
@@ -6728,7 +6962,7 @@
       <c r="M248" s="15"/>
       <c r="N248" s="16"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14">
       <c r="A249" s="12"/>
       <c r="B249" s="13"/>
       <c r="C249" s="13"/>
@@ -6750,7 +6984,7 @@
       <c r="M249" s="15"/>
       <c r="N249" s="16"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14">
       <c r="A250" s="12"/>
       <c r="B250" s="13"/>
       <c r="C250" s="13"/>
@@ -6772,7 +7006,7 @@
       <c r="M250" s="15"/>
       <c r="N250" s="16"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14">
       <c r="A251" s="12"/>
       <c r="B251" s="13"/>
       <c r="C251" s="13"/>
@@ -6794,7 +7028,7 @@
       <c r="M251" s="15"/>
       <c r="N251" s="16"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14">
       <c r="A252" s="12"/>
       <c r="B252" s="13"/>
       <c r="C252" s="13"/>
@@ -6816,7 +7050,7 @@
       <c r="M252" s="15"/>
       <c r="N252" s="16"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14">
       <c r="A253" s="12"/>
       <c r="B253" s="13"/>
       <c r="C253" s="13"/>
@@ -6838,7 +7072,7 @@
       <c r="M253" s="15"/>
       <c r="N253" s="16"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14">
       <c r="A254" s="12"/>
       <c r="B254" s="13"/>
       <c r="C254" s="13"/>
@@ -6860,7 +7094,7 @@
       <c r="M254" s="15"/>
       <c r="N254" s="16"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14">
       <c r="A255" s="12"/>
       <c r="B255" s="13"/>
       <c r="C255" s="13"/>
@@ -6882,7 +7116,7 @@
       <c r="M255" s="15"/>
       <c r="N255" s="16"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14">
       <c r="A256" s="12"/>
       <c r="B256" s="13"/>
       <c r="C256" s="13"/>
@@ -6904,7 +7138,7 @@
       <c r="M256" s="15"/>
       <c r="N256" s="16"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14">
       <c r="A257" s="12"/>
       <c r="B257" s="13"/>
       <c r="C257" s="13"/>
@@ -6926,7 +7160,7 @@
       <c r="M257" s="15"/>
       <c r="N257" s="16"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14">
       <c r="A258" s="12"/>
       <c r="B258" s="13"/>
       <c r="C258" s="13"/>
@@ -6948,7 +7182,7 @@
       <c r="M258" s="15"/>
       <c r="N258" s="16"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14">
       <c r="A259" s="12"/>
       <c r="B259" s="13"/>
       <c r="C259" s="13"/>
@@ -6970,7 +7204,7 @@
       <c r="M259" s="15"/>
       <c r="N259" s="16"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14">
       <c r="A260" s="12"/>
       <c r="B260" s="13"/>
       <c r="C260" s="13"/>
@@ -6992,7 +7226,7 @@
       <c r="M260" s="15"/>
       <c r="N260" s="16"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14">
       <c r="A261" s="12"/>
       <c r="B261" s="13"/>
       <c r="C261" s="13"/>
@@ -7014,7 +7248,7 @@
       <c r="M261" s="15"/>
       <c r="N261" s="16"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14">
       <c r="A262" s="12"/>
       <c r="B262" s="13"/>
       <c r="C262" s="13"/>
@@ -7036,7 +7270,7 @@
       <c r="M262" s="15"/>
       <c r="N262" s="16"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14">
       <c r="A263" s="12"/>
       <c r="B263" s="13"/>
       <c r="C263" s="13"/>
@@ -7058,7 +7292,7 @@
       <c r="M263" s="15"/>
       <c r="N263" s="16"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14">
       <c r="A264" s="12"/>
       <c r="B264" s="13"/>
       <c r="C264" s="13"/>
@@ -7080,7 +7314,7 @@
       <c r="M264" s="15"/>
       <c r="N264" s="16"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14">
       <c r="A265" s="12"/>
       <c r="B265" s="13"/>
       <c r="C265" s="13"/>
@@ -7102,7 +7336,7 @@
       <c r="M265" s="15"/>
       <c r="N265" s="16"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14">
       <c r="A266" s="12"/>
       <c r="B266" s="13"/>
       <c r="C266" s="13"/>
@@ -7124,7 +7358,7 @@
       <c r="M266" s="15"/>
       <c r="N266" s="16"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14">
       <c r="A267" s="12"/>
       <c r="B267" s="13"/>
       <c r="C267" s="13"/>
@@ -7146,7 +7380,7 @@
       <c r="M267" s="15"/>
       <c r="N267" s="16"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14">
       <c r="A268" s="12"/>
       <c r="B268" s="13"/>
       <c r="C268" s="13"/>
@@ -7168,7 +7402,7 @@
       <c r="M268" s="15"/>
       <c r="N268" s="16"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14">
       <c r="A269" s="12"/>
       <c r="B269" s="13"/>
       <c r="C269" s="13"/>
@@ -7190,7 +7424,7 @@
       <c r="M269" s="15"/>
       <c r="N269" s="16"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14">
       <c r="A270" s="12"/>
       <c r="B270" s="13"/>
       <c r="C270" s="13"/>
@@ -7212,7 +7446,7 @@
       <c r="M270" s="15"/>
       <c r="N270" s="16"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14">
       <c r="A271" s="12"/>
       <c r="B271" s="13"/>
       <c r="C271" s="13"/>
@@ -7234,7 +7468,7 @@
       <c r="M271" s="15"/>
       <c r="N271" s="16"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14">
       <c r="A272" s="12"/>
       <c r="B272" s="13"/>
       <c r="C272" s="13"/>
@@ -7256,7 +7490,7 @@
       <c r="M272" s="15"/>
       <c r="N272" s="16"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14">
       <c r="A273" s="12"/>
       <c r="B273" s="13"/>
       <c r="C273" s="13"/>
@@ -7278,7 +7512,7 @@
       <c r="M273" s="15"/>
       <c r="N273" s="16"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14">
       <c r="A274" s="12"/>
       <c r="B274" s="13"/>
       <c r="C274" s="13"/>
@@ -7300,7 +7534,7 @@
       <c r="M274" s="15"/>
       <c r="N274" s="16"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14">
       <c r="A275" s="12"/>
       <c r="B275" s="13"/>
       <c r="C275" s="13"/>
@@ -7322,7 +7556,7 @@
       <c r="M275" s="15"/>
       <c r="N275" s="16"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14">
       <c r="A276" s="12"/>
       <c r="B276" s="13"/>
       <c r="C276" s="13"/>
@@ -7344,7 +7578,7 @@
       <c r="M276" s="15"/>
       <c r="N276" s="16"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14">
       <c r="A277" s="12"/>
       <c r="B277" s="13"/>
       <c r="C277" s="13"/>
@@ -7366,7 +7600,7 @@
       <c r="M277" s="15"/>
       <c r="N277" s="16"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14">
       <c r="A278" s="12"/>
       <c r="B278" s="13"/>
       <c r="C278" s="13"/>
@@ -7388,7 +7622,7 @@
       <c r="M278" s="15"/>
       <c r="N278" s="16"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14">
       <c r="A279" s="12"/>
       <c r="B279" s="13"/>
       <c r="C279" s="13"/>
@@ -7410,7 +7644,7 @@
       <c r="M279" s="15"/>
       <c r="N279" s="16"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14">
       <c r="A280" s="12"/>
       <c r="B280" s="13"/>
       <c r="C280" s="13"/>
@@ -7432,7 +7666,7 @@
       <c r="M280" s="15"/>
       <c r="N280" s="16"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14">
       <c r="A281" s="12"/>
       <c r="B281" s="13"/>
       <c r="C281" s="13"/>
@@ -7454,7 +7688,7 @@
       <c r="M281" s="15"/>
       <c r="N281" s="16"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14">
       <c r="A282" s="12"/>
       <c r="B282" s="13"/>
       <c r="C282" s="13"/>
@@ -7476,7 +7710,7 @@
       <c r="M282" s="15"/>
       <c r="N282" s="16"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14">
       <c r="A283" s="12"/>
       <c r="B283" s="13"/>
       <c r="C283" s="13"/>
@@ -7498,7 +7732,7 @@
       <c r="M283" s="15"/>
       <c r="N283" s="16"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14">
       <c r="A284" s="12"/>
       <c r="B284" s="13"/>
       <c r="C284" s="13"/>
@@ -7520,7 +7754,7 @@
       <c r="M284" s="15"/>
       <c r="N284" s="16"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14">
       <c r="A285" s="12"/>
       <c r="B285" s="13"/>
       <c r="C285" s="13"/>
@@ -7542,7 +7776,7 @@
       <c r="M285" s="15"/>
       <c r="N285" s="16"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14">
       <c r="A286" s="12"/>
       <c r="B286" s="13"/>
       <c r="C286" s="13"/>
@@ -7564,7 +7798,7 @@
       <c r="M286" s="15"/>
       <c r="N286" s="16"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14">
       <c r="A287" s="12"/>
       <c r="B287" s="13"/>
       <c r="C287" s="13"/>
@@ -7586,7 +7820,7 @@
       <c r="M287" s="15"/>
       <c r="N287" s="16"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14">
       <c r="A288" s="12"/>
       <c r="B288" s="13"/>
       <c r="C288" s="13"/>
@@ -7608,7 +7842,7 @@
       <c r="M288" s="15"/>
       <c r="N288" s="16"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14">
       <c r="A289" s="12"/>
       <c r="B289" s="13"/>
       <c r="C289" s="13"/>
@@ -7630,7 +7864,7 @@
       <c r="M289" s="15"/>
       <c r="N289" s="16"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14">
       <c r="A290" s="12"/>
       <c r="B290" s="13"/>
       <c r="C290" s="13"/>
@@ -7652,7 +7886,7 @@
       <c r="M290" s="15"/>
       <c r="N290" s="16"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14">
       <c r="A291" s="12"/>
       <c r="B291" s="13"/>
       <c r="C291" s="13"/>
@@ -7674,7 +7908,7 @@
       <c r="M291" s="15"/>
       <c r="N291" s="16"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14">
       <c r="A292" s="12"/>
       <c r="B292" s="13"/>
       <c r="C292" s="13"/>
@@ -7696,7 +7930,7 @@
       <c r="M292" s="15"/>
       <c r="N292" s="16"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14">
       <c r="A293" s="12"/>
       <c r="B293" s="13"/>
       <c r="C293" s="13"/>
@@ -7718,7 +7952,7 @@
       <c r="M293" s="15"/>
       <c r="N293" s="16"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14">
       <c r="A294" s="12"/>
       <c r="B294" s="13"/>
       <c r="C294" s="13"/>
@@ -7740,7 +7974,7 @@
       <c r="M294" s="15"/>
       <c r="N294" s="16"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14">
       <c r="A295" s="12"/>
       <c r="B295" s="13"/>
       <c r="C295" s="13"/>
@@ -7762,7 +7996,7 @@
       <c r="M295" s="15"/>
       <c r="N295" s="16"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14">
       <c r="A296" s="12"/>
       <c r="B296" s="13"/>
       <c r="C296" s="13"/>
@@ -7784,7 +8018,7 @@
       <c r="M296" s="15"/>
       <c r="N296" s="16"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14">
       <c r="A297" s="12"/>
       <c r="B297" s="13"/>
       <c r="C297" s="13"/>
@@ -7806,7 +8040,7 @@
       <c r="M297" s="15"/>
       <c r="N297" s="16"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14">
       <c r="A298" s="12"/>
       <c r="B298" s="13"/>
       <c r="C298" s="13"/>
@@ -7828,7 +8062,7 @@
       <c r="M298" s="15"/>
       <c r="N298" s="16"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14">
       <c r="A299" s="12"/>
       <c r="B299" s="13"/>
       <c r="C299" s="13"/>
@@ -7850,7 +8084,7 @@
       <c r="M299" s="15"/>
       <c r="N299" s="16"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14">
       <c r="A300" s="12"/>
       <c r="B300" s="13"/>
       <c r="C300" s="13"/>
@@ -7872,7 +8106,7 @@
       <c r="M300" s="15"/>
       <c r="N300" s="16"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14">
       <c r="A301" s="12"/>
       <c r="B301" s="13"/>
       <c r="C301" s="13"/>
@@ -7894,7 +8128,7 @@
       <c r="M301" s="15"/>
       <c r="N301" s="16"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14">
       <c r="A302" s="12"/>
       <c r="B302" s="13"/>
       <c r="C302" s="13"/>
@@ -7916,7 +8150,7 @@
       <c r="M302" s="15"/>
       <c r="N302" s="16"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14">
       <c r="A303" s="12"/>
       <c r="B303" s="13"/>
       <c r="C303" s="13"/>
@@ -7938,7 +8172,7 @@
       <c r="M303" s="15"/>
       <c r="N303" s="16"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14">
       <c r="A304" s="12"/>
       <c r="B304" s="13"/>
       <c r="C304" s="13"/>
@@ -7960,7 +8194,7 @@
       <c r="M304" s="15"/>
       <c r="N304" s="16"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14">
       <c r="A305" s="12"/>
       <c r="B305" s="13"/>
       <c r="C305" s="13"/>
@@ -7982,7 +8216,7 @@
       <c r="M305" s="15"/>
       <c r="N305" s="16"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14">
       <c r="A306" s="12"/>
       <c r="B306" s="13"/>
       <c r="C306" s="13"/>
@@ -8004,7 +8238,7 @@
       <c r="M306" s="15"/>
       <c r="N306" s="16"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14">
       <c r="A307" s="12"/>
       <c r="B307" s="13"/>
       <c r="C307" s="13"/>
@@ -8026,7 +8260,7 @@
       <c r="M307" s="15"/>
       <c r="N307" s="16"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14">
       <c r="A308" s="12"/>
       <c r="B308" s="13"/>
       <c r="C308" s="13"/>
@@ -8048,7 +8282,7 @@
       <c r="M308" s="15"/>
       <c r="N308" s="16"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14">
       <c r="A309" s="12"/>
       <c r="B309" s="13"/>
       <c r="C309" s="13"/>
@@ -8070,7 +8304,7 @@
       <c r="M309" s="15"/>
       <c r="N309" s="16"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14">
       <c r="A310" s="12"/>
       <c r="B310" s="13"/>
       <c r="C310" s="13"/>
@@ -8092,7 +8326,7 @@
       <c r="M310" s="15"/>
       <c r="N310" s="16"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14">
       <c r="A311" s="12"/>
       <c r="B311" s="13"/>
       <c r="C311" s="13"/>
@@ -8114,7 +8348,7 @@
       <c r="M311" s="15"/>
       <c r="N311" s="16"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14">
       <c r="A312" s="12"/>
       <c r="B312" s="13"/>
       <c r="C312" s="13"/>
@@ -8136,7 +8370,7 @@
       <c r="M312" s="15"/>
       <c r="N312" s="16"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14">
       <c r="A313" s="12"/>
       <c r="B313" s="13"/>
       <c r="C313" s="13"/>
@@ -8158,7 +8392,7 @@
       <c r="M313" s="15"/>
       <c r="N313" s="16"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14">
       <c r="A314" s="12"/>
       <c r="B314" s="13"/>
       <c r="C314" s="13"/>
@@ -8180,7 +8414,7 @@
       <c r="M314" s="15"/>
       <c r="N314" s="16"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14">
       <c r="A315" s="12"/>
       <c r="B315" s="13"/>
       <c r="C315" s="13"/>
@@ -8202,7 +8436,7 @@
       <c r="M315" s="15"/>
       <c r="N315" s="16"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14">
       <c r="A316" s="12"/>
       <c r="B316" s="13"/>
       <c r="C316" s="13"/>
@@ -8224,7 +8458,7 @@
       <c r="M316" s="15"/>
       <c r="N316" s="16"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14">
       <c r="A317" s="12"/>
       <c r="B317" s="13"/>
       <c r="C317" s="13"/>
@@ -8246,7 +8480,7 @@
       <c r="M317" s="15"/>
       <c r="N317" s="16"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14">
       <c r="A318" s="12"/>
       <c r="B318" s="13"/>
       <c r="C318" s="13"/>
@@ -8268,7 +8502,7 @@
       <c r="M318" s="15"/>
       <c r="N318" s="16"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14">
       <c r="A319" s="12"/>
       <c r="B319" s="13"/>
       <c r="C319" s="13"/>
@@ -8290,7 +8524,7 @@
       <c r="M319" s="15"/>
       <c r="N319" s="16"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14">
       <c r="A320" s="12"/>
       <c r="B320" s="13"/>
       <c r="C320" s="13"/>
@@ -8312,7 +8546,7 @@
       <c r="M320" s="15"/>
       <c r="N320" s="16"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14">
       <c r="A321" s="12"/>
       <c r="B321" s="13"/>
       <c r="C321" s="13"/>
@@ -8334,7 +8568,7 @@
       <c r="M321" s="15"/>
       <c r="N321" s="16"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14">
       <c r="A322" s="12"/>
       <c r="B322" s="13"/>
       <c r="C322" s="13"/>
@@ -8356,7 +8590,7 @@
       <c r="M322" s="15"/>
       <c r="N322" s="16"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14">
       <c r="A323" s="12"/>
       <c r="B323" s="13"/>
       <c r="C323" s="13"/>
@@ -8378,7 +8612,7 @@
       <c r="M323" s="15"/>
       <c r="N323" s="16"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14">
       <c r="A324" s="12"/>
       <c r="B324" s="13"/>
       <c r="C324" s="13"/>
@@ -8400,7 +8634,7 @@
       <c r="M324" s="15"/>
       <c r="N324" s="16"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14">
       <c r="A325" s="12"/>
       <c r="B325" s="13"/>
       <c r="C325" s="13"/>
@@ -8422,7 +8656,7 @@
       <c r="M325" s="15"/>
       <c r="N325" s="16"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14">
       <c r="A326" s="12"/>
       <c r="B326" s="13"/>
       <c r="C326" s="13"/>
@@ -8444,7 +8678,7 @@
       <c r="M326" s="15"/>
       <c r="N326" s="16"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14">
       <c r="A327" s="12"/>
       <c r="B327" s="13"/>
       <c r="C327" s="13"/>
@@ -8466,7 +8700,7 @@
       <c r="M327" s="15"/>
       <c r="N327" s="16"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14">
       <c r="A328" s="12"/>
       <c r="B328" s="13"/>
       <c r="C328" s="13"/>
@@ -8488,7 +8722,7 @@
       <c r="M328" s="15"/>
       <c r="N328" s="16"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14">
       <c r="A329" s="12"/>
       <c r="B329" s="13"/>
       <c r="C329" s="13"/>
@@ -8510,7 +8744,7 @@
       <c r="M329" s="15"/>
       <c r="N329" s="16"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14">
       <c r="A330" s="12"/>
       <c r="B330" s="13"/>
       <c r="C330" s="13"/>
@@ -8532,7 +8766,7 @@
       <c r="M330" s="15"/>
       <c r="N330" s="16"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14">
       <c r="A331" s="12"/>
       <c r="B331" s="13"/>
       <c r="C331" s="13"/>
@@ -8554,7 +8788,7 @@
       <c r="M331" s="15"/>
       <c r="N331" s="16"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14">
       <c r="A332" s="12"/>
       <c r="B332" s="13"/>
       <c r="C332" s="13"/>
@@ -8576,7 +8810,7 @@
       <c r="M332" s="15"/>
       <c r="N332" s="16"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14">
       <c r="A333" s="12"/>
       <c r="B333" s="13"/>
       <c r="C333" s="13"/>
@@ -8598,7 +8832,7 @@
       <c r="M333" s="15"/>
       <c r="N333" s="16"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14">
       <c r="A334" s="12"/>
       <c r="B334" s="13"/>
       <c r="C334" s="13"/>
@@ -8620,7 +8854,7 @@
       <c r="M334" s="15"/>
       <c r="N334" s="16"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14">
       <c r="A335" s="12"/>
       <c r="B335" s="13"/>
       <c r="C335" s="13"/>
@@ -8642,7 +8876,7 @@
       <c r="M335" s="15"/>
       <c r="N335" s="16"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14">
       <c r="A336" s="12"/>
       <c r="B336" s="13"/>
       <c r="C336" s="13"/>
@@ -8664,7 +8898,7 @@
       <c r="M336" s="15"/>
       <c r="N336" s="16"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14">
       <c r="A337" s="12"/>
       <c r="B337" s="13"/>
       <c r="C337" s="13"/>
@@ -8686,7 +8920,7 @@
       <c r="M337" s="15"/>
       <c r="N337" s="16"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14">
       <c r="A338" s="12"/>
       <c r="B338" s="13"/>
       <c r="C338" s="13"/>
@@ -8708,7 +8942,7 @@
       <c r="M338" s="15"/>
       <c r="N338" s="16"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14">
       <c r="A339" s="12"/>
       <c r="B339" s="13"/>
       <c r="C339" s="13"/>
@@ -8730,7 +8964,7 @@
       <c r="M339" s="15"/>
       <c r="N339" s="16"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14">
       <c r="A340" s="12"/>
       <c r="B340" s="13"/>
       <c r="C340" s="13"/>
@@ -8752,7 +8986,7 @@
       <c r="M340" s="15"/>
       <c r="N340" s="16"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14">
       <c r="A341" s="12"/>
       <c r="B341" s="13"/>
       <c r="C341" s="13"/>
@@ -8774,7 +9008,7 @@
       <c r="M341" s="15"/>
       <c r="N341" s="16"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14">
       <c r="A342" s="12"/>
       <c r="B342" s="13"/>
       <c r="C342" s="13"/>
@@ -8796,7 +9030,7 @@
       <c r="M342" s="15"/>
       <c r="N342" s="16"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14">
       <c r="A343" s="12"/>
       <c r="B343" s="13"/>
       <c r="C343" s="13"/>
@@ -8818,7 +9052,7 @@
       <c r="M343" s="15"/>
       <c r="N343" s="16"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14">
       <c r="A344" s="12"/>
       <c r="B344" s="13"/>
       <c r="C344" s="13"/>
@@ -8840,7 +9074,7 @@
       <c r="M344" s="15"/>
       <c r="N344" s="16"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14">
       <c r="A345" s="12"/>
       <c r="B345" s="13"/>
       <c r="C345" s="13"/>
@@ -8862,7 +9096,7 @@
       <c r="M345" s="15"/>
       <c r="N345" s="16"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14">
       <c r="A346" s="12"/>
       <c r="B346" s="13"/>
       <c r="C346" s="13"/>
@@ -8884,7 +9118,7 @@
       <c r="M346" s="15"/>
       <c r="N346" s="16"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14">
       <c r="A347" s="12"/>
       <c r="B347" s="13"/>
       <c r="C347" s="13"/>
@@ -8906,7 +9140,7 @@
       <c r="M347" s="15"/>
       <c r="N347" s="16"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14">
       <c r="A348" s="12"/>
       <c r="B348" s="13"/>
       <c r="C348" s="13"/>
@@ -8928,7 +9162,7 @@
       <c r="M348" s="15"/>
       <c r="N348" s="16"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14">
       <c r="A349" s="12"/>
       <c r="B349" s="13"/>
       <c r="C349" s="13"/>
@@ -8950,7 +9184,7 @@
       <c r="M349" s="15"/>
       <c r="N349" s="16"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14">
       <c r="A350" s="12"/>
       <c r="B350" s="13"/>
       <c r="C350" s="13"/>
@@ -8972,7 +9206,7 @@
       <c r="M350" s="15"/>
       <c r="N350" s="16"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14">
       <c r="A351" s="12"/>
       <c r="B351" s="13"/>
       <c r="C351" s="13"/>
@@ -8994,7 +9228,7 @@
       <c r="M351" s="15"/>
       <c r="N351" s="16"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14">
       <c r="A352" s="12"/>
       <c r="B352" s="13"/>
       <c r="C352" s="13"/>
@@ -9016,7 +9250,7 @@
       <c r="M352" s="15"/>
       <c r="N352" s="16"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14">
       <c r="A353" s="12"/>
       <c r="B353" s="13"/>
       <c r="C353" s="13"/>
@@ -9038,7 +9272,7 @@
       <c r="M353" s="15"/>
       <c r="N353" s="16"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14">
       <c r="A354" s="12"/>
       <c r="B354" s="13"/>
       <c r="C354" s="13"/>
@@ -9060,7 +9294,7 @@
       <c r="M354" s="15"/>
       <c r="N354" s="16"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14">
       <c r="A355" s="12"/>
       <c r="B355" s="13"/>
       <c r="C355" s="13"/>
@@ -9082,7 +9316,7 @@
       <c r="M355" s="15"/>
       <c r="N355" s="16"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14">
       <c r="A356" s="12"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13"/>
@@ -9104,7 +9338,7 @@
       <c r="M356" s="15"/>
       <c r="N356" s="16"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14">
       <c r="A357" s="12"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13"/>
@@ -9126,7 +9360,7 @@
       <c r="M357" s="15"/>
       <c r="N357" s="16"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14">
       <c r="A358" s="12"/>
       <c r="B358" s="13"/>
       <c r="C358" s="13"/>
@@ -9148,7 +9382,7 @@
       <c r="M358" s="15"/>
       <c r="N358" s="16"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14">
       <c r="A359" s="12"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13"/>
@@ -9170,7 +9404,7 @@
       <c r="M359" s="15"/>
       <c r="N359" s="16"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14">
       <c r="A360" s="12"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13"/>
@@ -9192,7 +9426,7 @@
       <c r="M360" s="15"/>
       <c r="N360" s="16"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14">
       <c r="A361" s="12"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
@@ -9214,7 +9448,7 @@
       <c r="M361" s="15"/>
       <c r="N361" s="16"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14">
       <c r="A362" s="12"/>
       <c r="B362" s="13"/>
       <c r="C362" s="13"/>
@@ -9236,7 +9470,7 @@
       <c r="M362" s="15"/>
       <c r="N362" s="16"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14">
       <c r="A363" s="12"/>
       <c r="B363" s="13"/>
       <c r="C363" s="13"/>
@@ -9258,7 +9492,7 @@
       <c r="M363" s="15"/>
       <c r="N363" s="16"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14">
       <c r="A364" s="12"/>
       <c r="B364" s="13"/>
       <c r="C364" s="13"/>
@@ -9280,7 +9514,7 @@
       <c r="M364" s="15"/>
       <c r="N364" s="16"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14">
       <c r="A365" s="12"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13"/>
@@ -9302,7 +9536,7 @@
       <c r="M365" s="15"/>
       <c r="N365" s="16"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14">
       <c r="A366" s="12"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13"/>
@@ -9324,7 +9558,7 @@
       <c r="M366" s="15"/>
       <c r="N366" s="16"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14">
       <c r="A367" s="12"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13"/>
@@ -9346,7 +9580,7 @@
       <c r="M367" s="15"/>
       <c r="N367" s="16"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14">
       <c r="A368" s="12"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13"/>
@@ -9368,7 +9602,7 @@
       <c r="M368" s="15"/>
       <c r="N368" s="16"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:14">
       <c r="A369" s="12"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13"/>
@@ -9390,7 +9624,7 @@
       <c r="M369" s="15"/>
       <c r="N369" s="16"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14">
       <c r="A370" s="12"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
@@ -9412,7 +9646,7 @@
       <c r="M370" s="15"/>
       <c r="N370" s="16"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14">
       <c r="A371" s="12"/>
       <c r="B371" s="13"/>
       <c r="C371" s="13"/>
@@ -9434,7 +9668,7 @@
       <c r="M371" s="15"/>
       <c r="N371" s="16"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14">
       <c r="A372" s="12"/>
       <c r="B372" s="13"/>
       <c r="C372" s="13"/>
@@ -9456,7 +9690,7 @@
       <c r="M372" s="15"/>
       <c r="N372" s="16"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14">
       <c r="A373" s="12"/>
       <c r="B373" s="13"/>
       <c r="C373" s="13"/>
@@ -9478,7 +9712,7 @@
       <c r="M373" s="15"/>
       <c r="N373" s="16"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14">
       <c r="A374" s="12"/>
       <c r="B374" s="13"/>
       <c r="C374" s="13"/>
@@ -9500,7 +9734,7 @@
       <c r="M374" s="15"/>
       <c r="N374" s="16"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14">
       <c r="A375" s="12"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
@@ -9522,7 +9756,7 @@
       <c r="M375" s="15"/>
       <c r="N375" s="16"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14">
       <c r="A376" s="12"/>
       <c r="B376" s="13"/>
       <c r="C376" s="13"/>
@@ -9544,7 +9778,7 @@
       <c r="M376" s="15"/>
       <c r="N376" s="16"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14">
       <c r="A377" s="12"/>
       <c r="B377" s="13"/>
       <c r="C377" s="13"/>
@@ -9566,7 +9800,7 @@
       <c r="M377" s="15"/>
       <c r="N377" s="16"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14">
       <c r="A378" s="12"/>
       <c r="B378" s="13"/>
       <c r="C378" s="13"/>
@@ -9588,7 +9822,7 @@
       <c r="M378" s="15"/>
       <c r="N378" s="16"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:14">
       <c r="A379" s="12"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
@@ -9610,7 +9844,7 @@
       <c r="M379" s="15"/>
       <c r="N379" s="16"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14">
       <c r="A380" s="12"/>
       <c r="B380" s="13"/>
       <c r="C380" s="13"/>
@@ -9632,7 +9866,7 @@
       <c r="M380" s="15"/>
       <c r="N380" s="16"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14">
       <c r="A381" s="12"/>
       <c r="B381" s="13"/>
       <c r="C381" s="13"/>
@@ -9654,7 +9888,7 @@
       <c r="M381" s="15"/>
       <c r="N381" s="16"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14">
       <c r="A382" s="12"/>
       <c r="B382" s="13"/>
       <c r="C382" s="13"/>
@@ -9676,7 +9910,7 @@
       <c r="M382" s="15"/>
       <c r="N382" s="16"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14">
       <c r="A383" s="12"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
@@ -9698,7 +9932,7 @@
       <c r="M383" s="15"/>
       <c r="N383" s="16"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14">
       <c r="A384" s="12"/>
       <c r="B384" s="13"/>
       <c r="C384" s="13"/>
@@ -9720,7 +9954,7 @@
       <c r="M384" s="15"/>
       <c r="N384" s="16"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14">
       <c r="A385" s="12"/>
       <c r="B385" s="13"/>
       <c r="C385" s="13"/>
@@ -9742,7 +9976,7 @@
       <c r="M385" s="15"/>
       <c r="N385" s="16"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14">
       <c r="A386" s="12"/>
       <c r="B386" s="13"/>
       <c r="C386" s="13"/>
@@ -9764,7 +9998,7 @@
       <c r="M386" s="15"/>
       <c r="N386" s="16"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14">
       <c r="A387" s="12"/>
       <c r="B387" s="13"/>
       <c r="C387" s="13"/>
@@ -9786,7 +10020,7 @@
       <c r="M387" s="15"/>
       <c r="N387" s="16"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14">
       <c r="A388" s="12"/>
       <c r="B388" s="13"/>
       <c r="C388" s="13"/>
@@ -9808,7 +10042,7 @@
       <c r="M388" s="15"/>
       <c r="N388" s="16"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14">
       <c r="A389" s="12"/>
       <c r="B389" s="13"/>
       <c r="C389" s="13"/>
@@ -9830,7 +10064,7 @@
       <c r="M389" s="15"/>
       <c r="N389" s="16"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14">
       <c r="A390" s="12"/>
       <c r="B390" s="13"/>
       <c r="C390" s="13"/>
@@ -9852,7 +10086,7 @@
       <c r="M390" s="15"/>
       <c r="N390" s="16"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14">
       <c r="A391" s="12"/>
       <c r="B391" s="13"/>
       <c r="C391" s="13"/>
@@ -9874,7 +10108,7 @@
       <c r="M391" s="15"/>
       <c r="N391" s="16"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14">
       <c r="A392" s="12"/>
       <c r="B392" s="13"/>
       <c r="C392" s="13"/>
@@ -9896,7 +10130,7 @@
       <c r="M392" s="15"/>
       <c r="N392" s="16"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14">
       <c r="A393" s="12"/>
       <c r="B393" s="13"/>
       <c r="C393" s="13"/>
@@ -9918,7 +10152,7 @@
       <c r="M393" s="15"/>
       <c r="N393" s="16"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14">
       <c r="A394" s="12"/>
       <c r="B394" s="13"/>
       <c r="C394" s="13"/>
@@ -9940,7 +10174,7 @@
       <c r="M394" s="15"/>
       <c r="N394" s="16"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14">
       <c r="A395" s="12"/>
       <c r="B395" s="13"/>
       <c r="C395" s="13"/>
@@ -9962,7 +10196,7 @@
       <c r="M395" s="15"/>
       <c r="N395" s="16"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14">
       <c r="A396" s="12"/>
       <c r="B396" s="13"/>
       <c r="C396" s="13"/>
@@ -9984,7 +10218,7 @@
       <c r="M396" s="15"/>
       <c r="N396" s="16"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14">
       <c r="A397" s="12"/>
       <c r="B397" s="13"/>
       <c r="C397" s="13"/>
@@ -10006,7 +10240,7 @@
       <c r="M397" s="15"/>
       <c r="N397" s="16"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14">
       <c r="A398" s="12"/>
       <c r="B398" s="13"/>
       <c r="C398" s="13"/>
@@ -10028,7 +10262,7 @@
       <c r="M398" s="15"/>
       <c r="N398" s="16"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14">
       <c r="A399" s="12"/>
       <c r="B399" s="13"/>
       <c r="C399" s="13"/>
@@ -10050,7 +10284,7 @@
       <c r="M399" s="15"/>
       <c r="N399" s="16"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14">
       <c r="A400" s="12"/>
       <c r="B400" s="13"/>
       <c r="C400" s="13"/>
@@ -10072,7 +10306,7 @@
       <c r="M400" s="15"/>
       <c r="N400" s="16"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14">
       <c r="A401" s="12"/>
       <c r="B401" s="13"/>
       <c r="C401" s="13"/>
